--- a/DSA_Tracker.xlsx
+++ b/DSA_Tracker.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="A:\3) BTECH  cybersecurity  2024-2028\Codes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D41DC4AE-3A90-499D-8E9A-1944AA31A3DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{223F0B51-1A5A-41E1-9D41-E40D347EB56D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="21">
   <si>
     <t>Date</t>
   </si>
@@ -113,6 +113,18 @@
       </rPr>
       <t>, allow at most 1 mismatch, build valid index sequences, and choose the lexicographically smallest one.</t>
     </r>
+  </si>
+  <si>
+    <t>Leetcode &amp; GFG</t>
+  </si>
+  <si>
+    <t>Dynamic programing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Similar question , we need to check possible combo and check max sum possible </t>
+  </si>
+  <si>
+    <t>Concept and idea are okish, couldn’t solve questions</t>
   </si>
 </sst>
 </file>
@@ -479,7 +491,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D101"/>
+  <dimension ref="A1:E101"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
@@ -488,7 +500,7 @@
     <col min="4" max="4" width="60" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:5">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -502,7 +514,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4">
+    <row r="2" spans="1:5">
       <c r="A2" s="2">
         <v>46242</v>
       </c>
@@ -516,59 +528,72 @@
         <v>16</v>
       </c>
     </row>
-    <row r="3" spans="1:4">
-      <c r="A3" s="2"/>
-      <c r="D3" s="3"/>
-    </row>
-    <row r="4" spans="1:4">
+    <row r="3" spans="1:5" ht="28.8">
+      <c r="A3" s="2">
+        <v>46243</v>
+      </c>
+      <c r="B3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="E3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
       <c r="A4" s="2"/>
       <c r="D4" s="3"/>
     </row>
-    <row r="5" spans="1:4">
+    <row r="5" spans="1:5">
       <c r="A5" s="2"/>
       <c r="D5" s="3"/>
     </row>
-    <row r="6" spans="1:4">
+    <row r="6" spans="1:5">
       <c r="A6" s="2"/>
       <c r="D6" s="3"/>
     </row>
-    <row r="7" spans="1:4">
+    <row r="7" spans="1:5">
       <c r="A7" s="2"/>
       <c r="D7" s="3"/>
     </row>
-    <row r="8" spans="1:4">
+    <row r="8" spans="1:5">
       <c r="A8" s="2"/>
       <c r="D8" s="3"/>
     </row>
-    <row r="9" spans="1:4">
+    <row r="9" spans="1:5">
       <c r="A9" s="2"/>
       <c r="D9" s="3"/>
     </row>
-    <row r="10" spans="1:4">
+    <row r="10" spans="1:5">
       <c r="A10" s="2"/>
       <c r="D10" s="3"/>
     </row>
-    <row r="11" spans="1:4">
+    <row r="11" spans="1:5">
       <c r="A11" s="2"/>
       <c r="D11" s="3"/>
     </row>
-    <row r="12" spans="1:4">
+    <row r="12" spans="1:5">
       <c r="A12" s="2"/>
       <c r="D12" s="3"/>
     </row>
-    <row r="13" spans="1:4">
+    <row r="13" spans="1:5">
       <c r="A13" s="2"/>
       <c r="D13" s="3"/>
     </row>
-    <row r="14" spans="1:4">
+    <row r="14" spans="1:5">
       <c r="A14" s="2"/>
       <c r="D14" s="3"/>
     </row>
-    <row r="15" spans="1:4">
+    <row r="15" spans="1:5">
       <c r="A15" s="2"/>
       <c r="D15" s="3"/>
     </row>
-    <row r="16" spans="1:4">
+    <row r="16" spans="1:5">
       <c r="A16" s="2"/>
       <c r="D16" s="3"/>
     </row>

--- a/DSA_Tracker.xlsx
+++ b/DSA_Tracker.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="A:\3) BTECH  cybersecurity  2024-2028\Codes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{223F0B51-1A5A-41E1-9D41-E40D347EB56D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A680D16-BC7A-4384-915D-365731EBD301}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="25">
   <si>
     <t>Date</t>
   </si>
@@ -125,6 +125,18 @@
   </si>
   <si>
     <t>Concept and idea are okish, couldn’t solve questions</t>
+  </si>
+  <si>
+    <t>Leetcode</t>
+  </si>
+  <si>
+    <t>Half cases done but finally ans seen</t>
+  </si>
+  <si>
+    <t>Contiguous Array</t>
+  </si>
+  <si>
+    <t>contiguous array</t>
   </si>
 </sst>
 </file>
@@ -546,8 +558,21 @@
       </c>
     </row>
     <row r="4" spans="1:5">
-      <c r="A4" s="2"/>
-      <c r="D4" s="3"/>
+      <c r="A4" s="2">
+        <v>46244</v>
+      </c>
+      <c r="B4" t="s">
+        <v>21</v>
+      </c>
+      <c r="C4" t="s">
+        <v>23</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="E4" t="s">
+        <v>22</v>
+      </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="2"/>

--- a/DSA_Tracker.xlsx
+++ b/DSA_Tracker.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="A:\3) BTECH  cybersecurity  2024-2028\Codes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A680D16-BC7A-4384-915D-365731EBD301}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F68AF37-372C-4C82-A095-3822AA836D6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="31">
   <si>
     <t>Date</t>
   </si>
@@ -137,6 +137,24 @@
   </si>
   <si>
     <t>contiguous array</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Leetcode pod</t>
+  </si>
+  <si>
+    <t xml:space="preserve">length of longest sub array </t>
+  </si>
+  <si>
+    <t>hashmap, array</t>
+  </si>
+  <si>
+    <t>completed</t>
+  </si>
+  <si>
+    <t>Min num prefix sum</t>
+  </si>
+  <si>
+    <t>Array</t>
   </si>
 </sst>
 </file>
@@ -575,12 +593,38 @@
       </c>
     </row>
     <row r="5" spans="1:5">
-      <c r="A5" s="2"/>
-      <c r="D5" s="3"/>
+      <c r="A5" s="2">
+        <v>46245</v>
+      </c>
+      <c r="B5" t="s">
+        <v>25</v>
+      </c>
+      <c r="C5" t="s">
+        <v>30</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E5" t="s">
+        <v>28</v>
+      </c>
     </row>
     <row r="6" spans="1:5">
-      <c r="A6" s="2"/>
-      <c r="D6" s="3"/>
+      <c r="A6" s="2">
+        <v>46246</v>
+      </c>
+      <c r="B6" t="s">
+        <v>25</v>
+      </c>
+      <c r="C6" t="s">
+        <v>27</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E6" t="s">
+        <v>28</v>
+      </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="2"/>

--- a/DSA_Tracker.xlsx
+++ b/DSA_Tracker.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="A:\3) BTECH  cybersecurity  2024-2028\Codes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F68AF37-372C-4C82-A095-3822AA836D6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE0A9293-7E08-49FB-BBEB-890D6E5DA979}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="37">
   <si>
     <t>Date</t>
   </si>
@@ -155,6 +155,24 @@
   </si>
   <si>
     <t>Array</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Leetcode pod </t>
+  </si>
+  <si>
+    <t>tree and array</t>
+  </si>
+  <si>
+    <t>Brute force completed</t>
+  </si>
+  <si>
+    <t>Need to change char in string and find longest subarray with one repeating only</t>
+  </si>
+  <si>
+    <t>Striver</t>
+  </si>
+  <si>
+    <t>longest palindrome subarray</t>
   </si>
 </sst>
 </file>
@@ -626,13 +644,39 @@
         <v>28</v>
       </c>
     </row>
-    <row r="7" spans="1:5">
-      <c r="A7" s="2"/>
-      <c r="D7" s="3"/>
+    <row r="7" spans="1:5" ht="28.8">
+      <c r="A7" s="2">
+        <v>46247</v>
+      </c>
+      <c r="B7" t="s">
+        <v>31</v>
+      </c>
+      <c r="C7" t="s">
+        <v>32</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="E7" t="s">
+        <v>33</v>
+      </c>
     </row>
     <row r="8" spans="1:5">
-      <c r="A8" s="2"/>
-      <c r="D8" s="3"/>
+      <c r="A8" s="2">
+        <v>46247</v>
+      </c>
+      <c r="B8" t="s">
+        <v>35</v>
+      </c>
+      <c r="C8" t="s">
+        <v>15</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="E8" t="s">
+        <v>28</v>
+      </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="2"/>

--- a/DSA_Tracker.xlsx
+++ b/DSA_Tracker.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="A:\3) BTECH  cybersecurity  2024-2028\Codes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE0A9293-7E08-49FB-BBEB-890D6E5DA979}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97EAEB85-2EA8-4163-BC13-540B2BB3ECAA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -19,12 +19,23 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'DSA Tracker'!$A$1:$D$101</definedName>
   </definedNames>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="46">
   <si>
     <t>Date</t>
   </si>
@@ -173,6 +184,33 @@
   </si>
   <si>
     <t>longest palindrome subarray</t>
+  </si>
+  <si>
+    <t>14-Aug &lt;--&gt; 24-Aug</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Exams </t>
+  </si>
+  <si>
+    <t>Leet</t>
+  </si>
+  <si>
+    <t>Hash Set</t>
+  </si>
+  <si>
+    <t>Smallest multiple</t>
+  </si>
+  <si>
+    <t>Completed</t>
+  </si>
+  <si>
+    <t>String</t>
+  </si>
+  <si>
+    <t>Beautiful string shortest</t>
+  </si>
+  <si>
+    <t>Completes</t>
   </si>
 </sst>
 </file>
@@ -679,20 +717,62 @@
       </c>
     </row>
     <row r="9" spans="1:5">
-      <c r="A9" s="2"/>
-      <c r="D9" s="3"/>
+      <c r="A9" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="B9" t="e">
+        <f>--C9</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="C9" t="e">
+        <f>-- D9</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="D9" s="3" t="e">
+        <f>--E9</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="E9" t="s">
+        <v>38</v>
+      </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="2"/>
       <c r="D10" s="3"/>
     </row>
     <row r="11" spans="1:5">
-      <c r="A11" s="2"/>
-      <c r="D11" s="3"/>
+      <c r="A11" s="2">
+        <v>46259</v>
+      </c>
+      <c r="B11" t="s">
+        <v>39</v>
+      </c>
+      <c r="C11" t="s">
+        <v>40</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="E11" t="s">
+        <v>42</v>
+      </c>
     </row>
     <row r="12" spans="1:5">
-      <c r="A12" s="2"/>
-      <c r="D12" s="3"/>
+      <c r="A12" s="2">
+        <v>46260</v>
+      </c>
+      <c r="B12" t="s">
+        <v>39</v>
+      </c>
+      <c r="C12" t="s">
+        <v>43</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="E12" t="s">
+        <v>45</v>
+      </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13" s="2"/>

--- a/DSA_Tracker.xlsx
+++ b/DSA_Tracker.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="A:\3) BTECH  cybersecurity  2024-2028\Codes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97EAEB85-2EA8-4163-BC13-540B2BB3ECAA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9AC15204-FB78-4FCC-93AA-8A4A3B228E75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="6888" yWindow="996" windowWidth="17280" windowHeight="9420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DSA Tracker" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="47">
   <si>
     <t>Date</t>
   </si>
@@ -211,6 +211,9 @@
   </si>
   <si>
     <t>Completes</t>
+  </si>
+  <si>
+    <t>TCS volunteer</t>
   </si>
 </sst>
 </file>
@@ -775,8 +778,21 @@
       </c>
     </row>
     <row r="13" spans="1:5">
-      <c r="A13" s="2"/>
-      <c r="D13" s="3"/>
+      <c r="A13" s="2">
+        <v>46261</v>
+      </c>
+      <c r="B13" t="e">
+        <v>#VALUE!</v>
+      </c>
+      <c r="C13" t="e">
+        <v>#VALUE!</v>
+      </c>
+      <c r="D13" s="3" t="e">
+        <v>#VALUE!</v>
+      </c>
+      <c r="E13" t="s">
+        <v>46</v>
+      </c>
     </row>
     <row r="14" spans="1:5">
       <c r="A14" s="2"/>

--- a/DSA_Tracker.xlsx
+++ b/DSA_Tracker.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="A:\3) BTECH  cybersecurity  2024-2028\Codes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9AC15204-FB78-4FCC-93AA-8A4A3B228E75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08612AB0-D2B2-4773-87BD-A06D296E2424}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6888" yWindow="996" windowWidth="17280" windowHeight="9420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DSA Tracker" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="47">
   <si>
     <t>Date</t>
   </si>
@@ -795,12 +795,38 @@
       </c>
     </row>
     <row r="14" spans="1:5">
-      <c r="A14" s="2"/>
-      <c r="D14" s="3"/>
+      <c r="A14" s="2">
+        <v>46262</v>
+      </c>
+      <c r="B14" t="e">
+        <v>#VALUE!</v>
+      </c>
+      <c r="C14" t="e">
+        <v>#VALUE!</v>
+      </c>
+      <c r="D14" t="e">
+        <v>#VALUE!</v>
+      </c>
+      <c r="E14" t="s">
+        <v>46</v>
+      </c>
     </row>
     <row r="15" spans="1:5">
-      <c r="A15" s="2"/>
-      <c r="D15" s="3"/>
+      <c r="A15" s="2">
+        <v>46262</v>
+      </c>
+      <c r="B15" t="e">
+        <v>#VALUE!</v>
+      </c>
+      <c r="C15" t="e">
+        <v>#VALUE!</v>
+      </c>
+      <c r="D15" t="e">
+        <v>#VALUE!</v>
+      </c>
+      <c r="E15" t="s">
+        <v>46</v>
+      </c>
     </row>
     <row r="16" spans="1:5">
       <c r="A16" s="2"/>
@@ -1149,7 +1175,7 @@
   </sheetData>
   <autoFilter ref="A1:D101" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" sqref="B2:B101" xr:uid="{00000000-0002-0000-0000-000000000000}">
+    <dataValidation type="list" allowBlank="1" sqref="B2:B101 C14:D15" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"LeetCode,GFG,Striver Sheet"</formula1>
     </dataValidation>
   </dataValidations>

--- a/DSA_Tracker.xlsx
+++ b/DSA_Tracker.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="A:\3) BTECH  cybersecurity  2024-2028\Codes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08612AB0-D2B2-4773-87BD-A06D296E2424}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4A05960-8318-41FC-9E1E-5130425B18F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="55">
   <si>
     <t>Date</t>
   </si>
@@ -214,6 +214,30 @@
   </si>
   <si>
     <t>TCS volunteer</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> GFG POD</t>
+  </si>
+  <si>
+    <t>Ranks per marks</t>
+  </si>
+  <si>
+    <t>Based on the upper and lower bound find marks on ranked</t>
+  </si>
+  <si>
+    <t xml:space="preserve">leet and GFG </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Remove min max &amp;&amp; sum of beauty </t>
+  </si>
+  <si>
+    <t>Out of random number min num of stpes to delete min and max &amp;&amp; sum of beaty substring</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Striver sheet </t>
+  </si>
+  <si>
+    <t>Reverse String</t>
   </si>
 </sst>
 </file>
@@ -813,7 +837,7 @@
     </row>
     <row r="15" spans="1:5">
       <c r="A15" s="2">
-        <v>46262</v>
+        <v>46263</v>
       </c>
       <c r="B15" t="e">
         <v>#VALUE!</v>
@@ -829,70 +853,106 @@
       </c>
     </row>
     <row r="16" spans="1:5">
-      <c r="A16" s="2"/>
-      <c r="D16" s="3"/>
-    </row>
-    <row r="17" spans="1:4">
-      <c r="A17" s="2"/>
-      <c r="D17" s="3"/>
-    </row>
-    <row r="18" spans="1:4">
-      <c r="A18" s="2"/>
-      <c r="D18" s="3"/>
-    </row>
-    <row r="19" spans="1:4">
+      <c r="A16" s="2">
+        <v>46264</v>
+      </c>
+      <c r="B16" t="s">
+        <v>47</v>
+      </c>
+      <c r="C16" t="s">
+        <v>48</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="E16" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" ht="28.8">
+      <c r="A17" s="2">
+        <v>46265</v>
+      </c>
+      <c r="B17" t="s">
+        <v>50</v>
+      </c>
+      <c r="C17" t="s">
+        <v>51</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="E17" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="2">
+        <v>46266</v>
+      </c>
+      <c r="C18" t="s">
+        <v>53</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="E18" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
       <c r="A19" s="2"/>
       <c r="D19" s="3"/>
     </row>
-    <row r="20" spans="1:4">
+    <row r="20" spans="1:5">
       <c r="A20" s="2"/>
       <c r="D20" s="3"/>
     </row>
-    <row r="21" spans="1:4">
+    <row r="21" spans="1:5">
       <c r="A21" s="2"/>
       <c r="D21" s="3"/>
     </row>
-    <row r="22" spans="1:4">
+    <row r="22" spans="1:5">
       <c r="A22" s="2"/>
       <c r="D22" s="3"/>
     </row>
-    <row r="23" spans="1:4">
+    <row r="23" spans="1:5">
       <c r="A23" s="2"/>
       <c r="D23" s="3"/>
     </row>
-    <row r="24" spans="1:4">
+    <row r="24" spans="1:5">
       <c r="A24" s="2"/>
       <c r="D24" s="3"/>
     </row>
-    <row r="25" spans="1:4">
+    <row r="25" spans="1:5">
       <c r="A25" s="2"/>
       <c r="D25" s="3"/>
     </row>
-    <row r="26" spans="1:4">
+    <row r="26" spans="1:5">
       <c r="A26" s="2"/>
       <c r="D26" s="3"/>
     </row>
-    <row r="27" spans="1:4">
+    <row r="27" spans="1:5">
       <c r="A27" s="2"/>
       <c r="D27" s="3"/>
     </row>
-    <row r="28" spans="1:4">
+    <row r="28" spans="1:5">
       <c r="A28" s="2"/>
       <c r="D28" s="3"/>
     </row>
-    <row r="29" spans="1:4">
+    <row r="29" spans="1:5">
       <c r="A29" s="2"/>
       <c r="D29" s="3"/>
     </row>
-    <row r="30" spans="1:4">
+    <row r="30" spans="1:5">
       <c r="A30" s="2"/>
       <c r="D30" s="3"/>
     </row>
-    <row r="31" spans="1:4">
+    <row r="31" spans="1:5">
       <c r="A31" s="2"/>
       <c r="D31" s="3"/>
     </row>
-    <row r="32" spans="1:4">
+    <row r="32" spans="1:5">
       <c r="A32" s="2"/>
       <c r="D32" s="3"/>
     </row>

--- a/DSA_Tracker.xlsx
+++ b/DSA_Tracker.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="A:\3) BTECH  cybersecurity  2024-2028\Codes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4A05960-8318-41FC-9E1E-5130425B18F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E878D82E-F896-47ED-8D83-2FF9F382C88B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="57">
   <si>
     <t>Date</t>
   </si>
@@ -238,6 +238,12 @@
   </si>
   <si>
     <t>Reverse String</t>
+  </si>
+  <si>
+    <t>Hash Map</t>
+  </si>
+  <si>
+    <t>Computer occupation</t>
   </si>
 </sst>
 </file>
@@ -901,8 +907,21 @@
       </c>
     </row>
     <row r="19" spans="1:5">
-      <c r="A19" s="2"/>
-      <c r="D19" s="3"/>
+      <c r="A19" s="2">
+        <v>46236</v>
+      </c>
+      <c r="B19" t="s">
+        <v>50</v>
+      </c>
+      <c r="C19" t="s">
+        <v>55</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="E19" t="s">
+        <v>28</v>
+      </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="2"/>

--- a/DSA_Tracker.xlsx
+++ b/DSA_Tracker.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="A:\3) BTECH  cybersecurity  2024-2028\Codes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E878D82E-F896-47ED-8D83-2FF9F382C88B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54D0906C-3CAD-43EE-86FF-59229336A231}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="60">
   <si>
     <t>Date</t>
   </si>
@@ -244,6 +244,15 @@
   </si>
   <si>
     <t>Computer occupation</t>
+  </si>
+  <si>
+    <t>leet</t>
+  </si>
+  <si>
+    <t>Uniform_priority</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Array manipulation </t>
   </si>
 </sst>
 </file>
@@ -908,7 +917,7 @@
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="2">
-        <v>46236</v>
+        <v>46267</v>
       </c>
       <c r="B19" t="s">
         <v>50</v>
@@ -924,8 +933,21 @@
       </c>
     </row>
     <row r="20" spans="1:5">
-      <c r="A20" s="2"/>
-      <c r="D20" s="3"/>
+      <c r="A20" s="2">
+        <v>46268</v>
+      </c>
+      <c r="B20" t="s">
+        <v>57</v>
+      </c>
+      <c r="C20" t="s">
+        <v>58</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="E20" t="s">
+        <v>42</v>
+      </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="2"/>

--- a/DSA_Tracker.xlsx
+++ b/DSA_Tracker.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="A:\3) BTECH  cybersecurity  2024-2028\Codes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54D0906C-3CAD-43EE-86FF-59229336A231}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A2598D8-6E20-4600-B1C4-4B16773E7EC8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3852" yWindow="1512" windowWidth="17280" windowHeight="9420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DSA Tracker" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="61">
   <si>
     <t>Date</t>
   </si>
@@ -253,6 +253,9 @@
   </si>
   <si>
     <t xml:space="preserve">Array manipulation </t>
+  </si>
+  <si>
+    <t>bird_max_fruits &amp;&amp; small_stable</t>
   </si>
 </sst>
 </file>
@@ -950,8 +953,21 @@
       </c>
     </row>
     <row r="21" spans="1:5">
-      <c r="A21" s="2"/>
-      <c r="D21" s="3"/>
+      <c r="A21" s="2">
+        <v>46269</v>
+      </c>
+      <c r="B21" t="s">
+        <v>50</v>
+      </c>
+      <c r="C21" t="s">
+        <v>60</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="E21" t="s">
+        <v>42</v>
+      </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="2"/>

--- a/DSA_Tracker.xlsx
+++ b/DSA_Tracker.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="A:\3) BTECH  cybersecurity  2024-2028\Codes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A2598D8-6E20-4600-B1C4-4B16773E7EC8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78EEF1AE-12E7-4954-981B-764760483912}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3852" yWindow="1512" windowWidth="17280" windowHeight="9420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="62">
   <si>
     <t>Date</t>
   </si>
@@ -256,6 +256,9 @@
   </si>
   <si>
     <t>bird_max_fruits &amp;&amp; small_stable</t>
+  </si>
+  <si>
+    <t>small_stable_ii</t>
   </si>
 </sst>
 </file>
@@ -970,8 +973,21 @@
       </c>
     </row>
     <row r="22" spans="1:5">
-      <c r="A22" s="2"/>
-      <c r="D22" s="3"/>
+      <c r="A22" s="2">
+        <v>46270</v>
+      </c>
+      <c r="B22" t="s">
+        <v>57</v>
+      </c>
+      <c r="C22" t="s">
+        <v>61</v>
+      </c>
+      <c r="D22" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="E22" t="s">
+        <v>42</v>
+      </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="2"/>

--- a/DSA_Tracker.xlsx
+++ b/DSA_Tracker.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="A:\3) BTECH  cybersecurity  2024-2028\Codes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78EEF1AE-12E7-4954-981B-764760483912}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04235E96-D947-40B3-9FE7-9A7F9D2DA2BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3852" yWindow="1512" windowWidth="17280" windowHeight="9420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="64">
   <si>
     <t>Date</t>
   </si>
@@ -259,6 +259,12 @@
   </si>
   <si>
     <t>small_stable_ii</t>
+  </si>
+  <si>
+    <t>Linked list</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Introduction </t>
   </si>
 </sst>
 </file>
@@ -990,8 +996,21 @@
       </c>
     </row>
     <row r="23" spans="1:5">
-      <c r="A23" s="2"/>
-      <c r="D23" s="3"/>
+      <c r="A23" s="2">
+        <v>46271</v>
+      </c>
+      <c r="B23" t="s">
+        <v>35</v>
+      </c>
+      <c r="C23" t="s">
+        <v>62</v>
+      </c>
+      <c r="D23" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="E23" t="s">
+        <v>42</v>
+      </c>
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="2"/>

--- a/DSA_Tracker.xlsx
+++ b/DSA_Tracker.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="A:\3) BTECH  cybersecurity  2024-2028\Codes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04235E96-D947-40B3-9FE7-9A7F9D2DA2BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6AB65B8-E46E-4110-8C8B-5F80A7E50194}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3852" yWindow="1512" windowWidth="17280" windowHeight="9420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="65">
   <si>
     <t>Date</t>
   </si>
@@ -265,6 +265,9 @@
   </si>
   <si>
     <t xml:space="preserve">Introduction </t>
+  </si>
+  <si>
+    <t>Insertion</t>
   </si>
 </sst>
 </file>
@@ -1013,8 +1016,21 @@
       </c>
     </row>
     <row r="24" spans="1:5">
-      <c r="A24" s="2"/>
-      <c r="D24" s="3"/>
+      <c r="A24" s="2">
+        <v>46272</v>
+      </c>
+      <c r="B24" t="s">
+        <v>35</v>
+      </c>
+      <c r="C24" t="s">
+        <v>62</v>
+      </c>
+      <c r="D24" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="E24" t="s">
+        <v>42</v>
+      </c>
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="2"/>

--- a/DSA_Tracker.xlsx
+++ b/DSA_Tracker.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="A:\3) BTECH  cybersecurity  2024-2028\Codes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6AB65B8-E46E-4110-8C8B-5F80A7E50194}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C3B3A0B-5CC9-446C-AA81-26A7A3CCD95F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3852" yWindow="1512" windowWidth="17280" windowHeight="9420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="68">
   <si>
     <t>Date</t>
   </si>
@@ -268,6 +268,15 @@
   </si>
   <si>
     <t>Insertion</t>
+  </si>
+  <si>
+    <t>Striver &amp; leet</t>
+  </si>
+  <si>
+    <t>Linked list &amp; arrays</t>
+  </si>
+  <si>
+    <t>deletion &amp; noof comms</t>
   </si>
 </sst>
 </file>
@@ -1033,8 +1042,21 @@
       </c>
     </row>
     <row r="25" spans="1:5">
-      <c r="A25" s="2"/>
-      <c r="D25" s="3"/>
+      <c r="A25" s="2">
+        <v>46273</v>
+      </c>
+      <c r="B25" t="s">
+        <v>65</v>
+      </c>
+      <c r="C25" t="s">
+        <v>66</v>
+      </c>
+      <c r="D25" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="E25" t="s">
+        <v>42</v>
+      </c>
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="2"/>

--- a/DSA_Tracker.xlsx
+++ b/DSA_Tracker.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="A:\3) BTECH  cybersecurity  2024-2028\Codes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C3B3A0B-5CC9-446C-AA81-26A7A3CCD95F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6605BF84-631E-4D84-BAF4-0EA797AB1E02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3852" yWindow="1512" windowWidth="17280" windowHeight="9420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="70">
   <si>
     <t>Date</t>
   </si>
@@ -277,6 +277,12 @@
   </si>
   <si>
     <t>deletion &amp; noof comms</t>
+  </si>
+  <si>
+    <t>arrays &amp; linked list</t>
+  </si>
+  <si>
+    <t>length of ll &amp; noof commas ii</t>
   </si>
 </sst>
 </file>
@@ -1059,8 +1065,21 @@
       </c>
     </row>
     <row r="26" spans="1:5">
-      <c r="A26" s="2"/>
-      <c r="D26" s="3"/>
+      <c r="A26" s="2">
+        <v>46274</v>
+      </c>
+      <c r="B26" t="s">
+        <v>65</v>
+      </c>
+      <c r="C26" t="s">
+        <v>68</v>
+      </c>
+      <c r="D26" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="E26" t="s">
+        <v>42</v>
+      </c>
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="2"/>

--- a/DSA_Tracker.xlsx
+++ b/DSA_Tracker.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="A:\3) BTECH  cybersecurity  2024-2028\Codes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6605BF84-631E-4D84-BAF4-0EA797AB1E02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{65EFEA2D-2365-46F8-8C4C-C2C127F42046}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3852" yWindow="1512" windowWidth="17280" windowHeight="9420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="73">
   <si>
     <t>Date</t>
   </si>
@@ -283,6 +283,15 @@
   </si>
   <si>
     <t>length of ll &amp; noof commas ii</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GFG </t>
+  </si>
+  <si>
+    <t>Maths</t>
+  </si>
+  <si>
+    <t>GCD and Lcm</t>
   </si>
 </sst>
 </file>
@@ -1082,8 +1091,21 @@
       </c>
     </row>
     <row r="27" spans="1:5">
-      <c r="A27" s="2"/>
-      <c r="D27" s="3"/>
+      <c r="A27" s="2">
+        <v>46275</v>
+      </c>
+      <c r="B27" t="s">
+        <v>70</v>
+      </c>
+      <c r="C27" t="s">
+        <v>71</v>
+      </c>
+      <c r="D27" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="E27" t="s">
+        <v>42</v>
+      </c>
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="2"/>

--- a/DSA_Tracker.xlsx
+++ b/DSA_Tracker.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="A:\3) BTECH  cybersecurity  2024-2028\Codes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{65EFEA2D-2365-46F8-8C4C-C2C127F42046}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49A192C7-FF38-42CB-BEE1-07EBF3F566CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3852" yWindow="1512" windowWidth="17280" windowHeight="9420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="75">
   <si>
     <t>Date</t>
   </si>
@@ -293,6 +293,12 @@
   <si>
     <t>GCD and Lcm</t>
   </si>
+  <si>
+    <t xml:space="preserve">Maths </t>
+  </si>
+  <si>
+    <t>Values with Equal Array Remainders</t>
+  </si>
 </sst>
 </file>
 
@@ -301,7 +307,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="dd\-mmm\-yyyy"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -324,6 +330,11 @@
       <color theme="1"/>
       <name val="Arial Unicode MS"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -345,7 +356,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -356,6 +367,9 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1107,9 +1121,22 @@
         <v>42</v>
       </c>
     </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="2"/>
-      <c r="D28" s="3"/>
+    <row r="28" spans="1:5" ht="15.6">
+      <c r="A28" s="2">
+        <v>46276</v>
+      </c>
+      <c r="B28" t="s">
+        <v>70</v>
+      </c>
+      <c r="C28" t="s">
+        <v>73</v>
+      </c>
+      <c r="D28" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="E28" t="s">
+        <v>42</v>
+      </c>
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="2"/>
